--- a/sample-data/CRM历史项目表-脱敏适配样表.xlsx
+++ b/sample-data/CRM历史项目表-脱敏适配样表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-储备项目报备表（跟进中和呆滞）" sheetId="1" r:id="R7d100f9d00724e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-储备项目报备表（跟进中和呆滞）" sheetId="1" r:id="Rfadc7cd9dd88437e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -376,7 +376,7 @@
         <x:v>华东业务部</x:v>
       </x:c>
       <x:c r="B2" s="16" t="str">
-        <x:v>周岚</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="C2" s="16" t="str">
         <x:v>2026-05-10</x:v>
@@ -411,7 +411,7 @@
         <x:v>华南业务部</x:v>
       </x:c>
       <x:c r="B3" s="16" t="str">
-        <x:v>韩哲</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="C3" s="16" t="str">
         <x:v>2026-03-02</x:v>
@@ -446,7 +446,7 @@
         <x:v>华北业务部</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>叶宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
         <x:v>2026-01-18</x:v>
@@ -481,7 +481,7 @@
         <x:v>华中业务部</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>许安</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
         <x:v>2026-06-03</x:v>
@@ -516,7 +516,7 @@
         <x:v>华东业务部</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>周岚</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
         <x:v>2026-04-26</x:v>
@@ -551,7 +551,7 @@
         <x:v>华西业务部</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>宋敏</x:v>
+        <x:v>示例经理戊</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
         <x:v>2026-06-20</x:v>

--- a/sample-data/CRM历史项目表-脱敏适配样表.xlsx
+++ b/sample-data/CRM历史项目表-脱敏适配样表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-储备项目报备表（跟进中和呆滞）" sheetId="1" r:id="Rfadc7cd9dd88437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析表" sheetId="1" r:id="Rcf5aea2b6c7f492c"/>
   </x:sheets>
 </x:workbook>
 </file>
